--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130321892</v>
+        <v>130325708</v>
       </c>
       <c r="B8" t="n">
         <v>91749</v>
@@ -1388,14 +1388,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>L. Uringe, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662756</v>
+        <v>662731</v>
       </c>
       <c r="R8" t="n">
-        <v>6557328</v>
+        <v>6557334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,19 +1452,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130325708</v>
+        <v>130321892</v>
       </c>
       <c r="B9" t="n">
         <v>91749</v>
@@ -1495,14 +1495,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>L. Uringe, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662731</v>
+        <v>662756</v>
       </c>
       <c r="R9" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,12 +1559,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1683,48 +1683,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57820</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R11" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1771,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,68 +1786,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R12" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,12 +1893,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>5362</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R4" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>5362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,39 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R5" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130323421</v>
+        <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,32 +1154,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662910</v>
+        <v>662676</v>
       </c>
       <c r="R6" t="n">
-        <v>6557370</v>
+        <v>6557301</v>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130322103</v>
+        <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>91749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,39 +1249,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>L. Uringe, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662676</v>
+        <v>662731</v>
       </c>
       <c r="R7" t="n">
-        <v>6557301</v>
+        <v>6557334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130325708</v>
+        <v>130321892</v>
       </c>
       <c r="B8" t="n">
         <v>91749</v>
@@ -1388,14 +1376,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>L. Uringe, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662731</v>
+        <v>662756</v>
       </c>
       <c r="R8" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1440,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130321892</v>
+        <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>91749</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1463,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662756</v>
+        <v>662870</v>
       </c>
       <c r="R9" t="n">
-        <v>6557328</v>
+        <v>6557386</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1537,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,50 +1564,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130321196</v>
+        <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662870</v>
+        <v>662826</v>
       </c>
       <c r="R10" t="n">
-        <v>6557386</v>
+        <v>6557361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,48 +1786,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130321327</v>
+        <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>57820</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>L Uringe3, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662826</v>
+        <v>662910</v>
       </c>
       <c r="R12" t="n">
-        <v>6557361</v>
+        <v>6557373</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1893,15 +1893,139 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130402099</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>övernattning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L Uringe, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>662910</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557370</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Övernattningshål lämpliga för bl.a. Entita.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>5362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,39 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R4" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B5" t="n">
-        <v>5362</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,34 +1025,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R5" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1564,56 +1564,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R10" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,60 +1659,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57820</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R11" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1564,48 +1564,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B10" t="n">
-        <v>57820</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R10" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,68 +1667,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R11" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1564,56 +1564,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R10" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,60 +1659,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57820</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R11" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>5362</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R4" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>5362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,39 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R5" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130321818</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130323414</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57820</v>
+        <v>57846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>58009</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>58009</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,48 +1564,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B10" t="n">
-        <v>57846</v>
+        <v>58011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R10" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,68 +1667,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>58011</v>
+        <v>57846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R11" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130321818</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130323414</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130323424</v>
       </c>
       <c r="B10" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>57846</v>
+        <v>57848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>58009</v>
+        <v>58011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>58009</v>
+        <v>58011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130325708</v>
+        <v>130321892</v>
       </c>
       <c r="B7" t="n">
         <v>91782</v>
@@ -1269,14 +1269,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>L. Uringe, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662731</v>
+        <v>662756</v>
       </c>
       <c r="R7" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130321892</v>
+        <v>130325708</v>
       </c>
       <c r="B8" t="n">
         <v>91782</v>
@@ -1376,14 +1376,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>L. Uringe, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662756</v>
+        <v>662731</v>
       </c>
       <c r="R8" t="n">
-        <v>6557328</v>
+        <v>6557334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,12 +1440,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>5362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,39 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R4" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B5" t="n">
-        <v>5362</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,34 +1025,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R5" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1564,56 +1564,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>58013</v>
+        <v>57848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R10" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,60 +1659,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R11" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>5362</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R4" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>5362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,39 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R5" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130321892</v>
+        <v>130325708</v>
       </c>
       <c r="B7" t="n">
         <v>91782</v>
@@ -1269,14 +1269,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>L. Uringe, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662756</v>
+        <v>662731</v>
       </c>
       <c r="R7" t="n">
-        <v>6557328</v>
+        <v>6557334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,19 +1333,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130325708</v>
+        <v>130321892</v>
       </c>
       <c r="B8" t="n">
         <v>91782</v>
@@ -1376,14 +1376,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>L. Uringe, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662731</v>
+        <v>662756</v>
       </c>
       <c r="R8" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,12 +1440,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1564,48 +1564,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B10" t="n">
-        <v>57848</v>
+        <v>58013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R10" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,68 +1667,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>57848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R11" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130321818</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130323414</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,56 +1564,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>58013</v>
+        <v>57856</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R10" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,60 +1659,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R11" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>58011</v>
+        <v>58019</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>58011</v>
+        <v>58019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130321818</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130323414</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>5362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,39 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R4" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B5" t="n">
-        <v>5362</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,34 +1025,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R5" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1129,7 @@
         <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57856</v>
+        <v>57857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130321818</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130323414</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>130321914</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>130322103</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>130325708</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>130321892</v>
       </c>
       <c r="B8" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>130321196</v>
       </c>
       <c r="B9" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>130321327</v>
       </c>
       <c r="B10" t="n">
-        <v>57857</v>
+        <v>57858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>130323424</v>
       </c>
       <c r="B11" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321266</v>
+        <v>130321914</v>
       </c>
       <c r="B4" t="n">
-        <v>5362</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +918,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662835</v>
+        <v>662751</v>
       </c>
       <c r="R4" t="n">
-        <v>6557364</v>
+        <v>6557328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321914</v>
+        <v>130321266</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>5362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,39 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662751</v>
+        <v>662835</v>
       </c>
       <c r="R5" t="n">
-        <v>6557328</v>
+        <v>6557364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -1564,48 +1564,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130321327</v>
+        <v>130323424</v>
       </c>
       <c r="B10" t="n">
-        <v>57858</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662826</v>
+        <v>662784</v>
       </c>
       <c r="R10" t="n">
-        <v>6557361</v>
+        <v>6557363</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,68 +1667,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130323424</v>
+        <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>57858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662784</v>
+        <v>662826</v>
       </c>
       <c r="R11" t="n">
-        <v>6557363</v>
+        <v>6557361</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1774,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130321818</v>
+        <v>130321892</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662772</v>
+        <v>662756</v>
       </c>
       <c r="R2" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130323414</v>
+        <v>130325708</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,45 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>L. Uringe, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662796</v>
+        <v>662731</v>
       </c>
       <c r="R3" t="n">
-        <v>6557363</v>
+        <v>6557334</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Jens Ullenius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130321914</v>
+        <v>92673668</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,25 +917,35 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Uringe, Botkyrka, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662751</v>
+        <v>662589</v>
       </c>
       <c r="R4" t="n">
-        <v>6557328</v>
+        <v>6557274</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2021-04-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,57 +989,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130321266</v>
+        <v>130321818</v>
       </c>
       <c r="B5" t="n">
-        <v>5362</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662835</v>
+        <v>662772</v>
       </c>
       <c r="R5" t="n">
-        <v>6557364</v>
+        <v>6557334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,14 +1113,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130322103</v>
+        <v>130321888</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1162,14 +1149,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662676</v>
+        <v>662749</v>
       </c>
       <c r="R6" t="n">
-        <v>6557301</v>
+        <v>6557363</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,45 +1225,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130325708</v>
+        <v>130321914</v>
       </c>
       <c r="B7" t="n">
-        <v>91797</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>L. Uringe, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662731</v>
+        <v>662751</v>
       </c>
       <c r="R7" t="n">
-        <v>6557334</v>
+        <v>6557328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,57 +1325,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jens Ullenius</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130321892</v>
+        <v>130322103</v>
       </c>
       <c r="B8" t="n">
-        <v>91797</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662756</v>
+        <v>662676</v>
       </c>
       <c r="R8" t="n">
-        <v>6557328</v>
+        <v>6557301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1425,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,53 +1449,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130321196</v>
+        <v>130323414</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malmstugan, Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662870</v>
+        <v>662796</v>
       </c>
       <c r="R9" t="n">
-        <v>6557386</v>
+        <v>6557363</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1537,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,44 +1557,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130323424</v>
+        <v>130323416</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1603,17 +1608,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Malmstugan, Malmstugan, Srm</t>
+          <t>Malmstugan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662784</v>
+        <v>662791</v>
       </c>
       <c r="R10" t="n">
-        <v>6557363</v>
+        <v>6557389</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,7 +1687,7 @@
         <v>130321327</v>
       </c>
       <c r="B11" t="n">
-        <v>57858</v>
+        <v>57947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1794,7 @@
         <v>130323421</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1913,7 @@
         <v>130402099</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,6 +2031,693 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130321105</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Malmstugan, Malmstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>662838</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557394</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130321196</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Malmstugan, Malmstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>662870</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557386</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130322018</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>662703</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557323</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130323423</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Malmstugan, Malmstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>662831</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557394</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130323424</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Malmstugan, Malmstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>662784</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557363</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130325713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L. Uringe, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>662853</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557410</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jens Ullenius</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60416-2025 artfynd.xlsx
+++ b/artfynd/A 60416-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321892</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325708</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92673668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321818</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321888</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321914</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323414</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323416</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1788,6 +1838,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321327</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2031,6 +2091,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130402099</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2143,6 +2208,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321196</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322018</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2486,6 +2566,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323423</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2601,6 +2686,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323424</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2718,8 +2808,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>